--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>date</t>
   </si>
@@ -285,6 +285,81 @@
   </si>
   <si>
     <t>2025-10-03 17:59:37</t>
+  </si>
+  <si>
+    <t>2025-10-03 18:10:43</t>
+  </si>
+  <si>
+    <t>2025-10-03 18:10:44</t>
+  </si>
+  <si>
+    <t>2025-10-03 18:10:45</t>
+  </si>
+  <si>
+    <t>2025-10-06 12:38:24</t>
+  </si>
+  <si>
+    <t>2025-10-06 12:38:25</t>
+  </si>
+  <si>
+    <t>2025-10-06 12:38:26</t>
+  </si>
+  <si>
+    <t>10/03/2025</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:08</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:09</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:10</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:44</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:45</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:46</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:55</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:56</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:17:57</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:18:22</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:18:23</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:18:24</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:19:48</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:19:50</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:19:51</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:21:20</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:21:21</t>
+  </si>
+  <si>
+    <t>2025-10-06 20:21:22</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -2376,15 +2451,393 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
+        <v>82</v>
+      </c>
+      <c r="B92" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>83</v>
+      </c>
+      <c r="B93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>83</v>
+      </c>
+      <c r="B94" t="s">
+        <v>65</v>
+      </c>
+      <c r="C94" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B95" t="s">
+        <v>65</v>
+      </c>
+      <c r="C95" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" t="s">
+        <v>65</v>
+      </c>
+      <c r="C96" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>84</v>
+      </c>
+      <c r="B97" t="s">
+        <v>65</v>
+      </c>
+      <c r="C97" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>85</v>
+      </c>
+      <c r="B98" t="s">
+        <v>88</v>
+      </c>
+      <c r="C98" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>86</v>
+      </c>
+      <c r="B99" t="s">
+        <v>88</v>
+      </c>
+      <c r="C99" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>87</v>
+      </c>
+      <c r="B100" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>91</v>
+      </c>
+      <c r="B103" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104" t="s">
+        <v>88</v>
+      </c>
+      <c r="C104" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" t="s">
+        <v>88</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>94</v>
+      </c>
+      <c r="B106" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>95</v>
+      </c>
+      <c r="B107" t="s">
+        <v>88</v>
+      </c>
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>96</v>
+      </c>
+      <c r="B108" t="s">
+        <v>88</v>
+      </c>
+      <c r="C108" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109" t="s">
+        <v>88</v>
+      </c>
+      <c r="C109" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>98</v>
+      </c>
+      <c r="B110" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>99</v>
+      </c>
+      <c r="B111" t="s">
+        <v>88</v>
+      </c>
+      <c r="C111" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>100</v>
+      </c>
+      <c r="B112" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>101</v>
+      </c>
+      <c r="B113" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>103</v>
+      </c>
+      <c r="B115" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>104</v>
+      </c>
+      <c r="B116" t="s">
+        <v>88</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117" t="s">
+        <v>88</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>106</v>
+      </c>
+      <c r="B118" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" t="s">
+        <v>22</v>
+      </c>
+      <c r="D118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
         <v>66</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B119" t="s">
         <v>67</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C119" t="s">
         <v>68</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D119" t="s">
         <v>69</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_DATA\00_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\14-MarquisBook\excel_dockers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{1AD67346-F1D8-4A10-B55A-0F4FEE34EB76}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{1B193E48-6BF0-4438-85C1-22F39C7A431E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="10300" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView windowHeight="12975" windowWidth="21795" xWindow="-98" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-98"/>
   </bookViews>
   <sheets>
     <sheet name="resumeData" r:id="rId1" sheetId="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -261,6 +261,63 @@
   </si>
   <si>
     <t>2025-06-12 19:21:29</t>
+  </si>
+  <si>
+    <t>2025-10-07 11:23:54</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>2025-10-07 11:52:56</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:11:58</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:15:27</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:16:18</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:17:32</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:17:53</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:18:48</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:19:37</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:20:34</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:25:42</t>
+  </si>
+  <si>
+    <t>2025-10-08 15:12:49</t>
+  </si>
+  <si>
+    <t>10/03/2025</t>
+  </si>
+  <si>
+    <t>2025-10-08 15:56:31</t>
+  </si>
+  <si>
+    <t>2025-10-08 16:07:49</t>
+  </si>
+  <si>
+    <t>2025-10-08 16:09:39</t>
   </si>
 </sst>
 </file>
@@ -746,7 +803,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1068,16 +1125,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="24.1796875"/>
-    <col customWidth="1" max="2" min="2" width="24.90625"/>
+    <col customWidth="1" max="1" min="1" width="24.19921875"/>
+    <col customWidth="1" max="2" min="2" width="24.9296875"/>
     <col customWidth="1" max="3" min="3" width="26"/>
-    <col bestFit="1" customWidth="1" max="4" min="4" width="14.6328125"/>
+    <col bestFit="1" customWidth="1" max="4" min="4" width="14.59765625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1091,948 +1148,1157 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>11</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="1" t="s">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36">
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="1">
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42">
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50">
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>65</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54">
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
         <v>64</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56">
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>65</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58">
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
         <v>68</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>65</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>24</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60">
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="1">
+      <c r="C62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62">
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64">
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>24</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65">
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
         <v>72</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66">
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67">
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C83" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D83" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup copies="0" horizontalDpi="0" orientation="portrait" paperSize="0" verticalDpi="0"/>
+  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\14-MarquisBook\src\app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\14-MarquisBook\excel_dockers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{2530336A-D5B6-4AA1-ADCB-24B526302146}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{1B193E48-6BF0-4438-85C1-22F39C7A431E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="12975" windowWidth="21795" xWindow="-98" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-98"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>date</t>
   </si>
@@ -53,6 +53,18 @@
     <t>amount</t>
   </si>
   <si>
+    <t>${table:resumeData.date}</t>
+  </si>
+  <si>
+    <t>${table:resumeData.tradeDate}</t>
+  </si>
+  <si>
+    <t>${table:resumeData.origin}</t>
+  </si>
+  <si>
+    <t>${table:resumeData.amount}</t>
+  </si>
+  <si>
     <t>2025-05-22 10:34:52</t>
   </si>
   <si>
@@ -227,139 +239,109 @@
     <t>06/11/2025</t>
   </si>
   <si>
-    <t>2025-10-03 13:20:31</t>
-  </si>
-  <si>
-    <t>2025-10-03 13:20:32</t>
-  </si>
-  <si>
-    <t>2025-10-03 13:20:33</t>
-  </si>
-  <si>
-    <t>10/02/2025</t>
-  </si>
-  <si>
-    <t>${table:resumeData.date}</t>
-  </si>
-  <si>
-    <t>${table:resumeData.tradeDate}</t>
-  </si>
-  <si>
-    <t>${table:resumeData.origin}</t>
-  </si>
-  <si>
-    <t>${table:resumeData.amount}</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:23:52</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:23:53</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:38:20</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:38:21</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:38:51</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:38:52</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:48:08</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:48:09</t>
-  </si>
-  <si>
-    <t>2025-10-03 16:48:10</t>
-  </si>
-  <si>
-    <t>2025-10-03 17:59:35</t>
-  </si>
-  <si>
-    <t>2025-10-03 17:59:36</t>
-  </si>
-  <si>
-    <t>2025-10-03 17:59:37</t>
-  </si>
-  <si>
-    <t>2025-10-03 18:10:43</t>
-  </si>
-  <si>
-    <t>2025-10-03 18:10:44</t>
-  </si>
-  <si>
-    <t>2025-10-03 18:10:45</t>
-  </si>
-  <si>
-    <t>2025-10-06 12:38:24</t>
-  </si>
-  <si>
-    <t>2025-10-06 12:38:25</t>
-  </si>
-  <si>
-    <t>2025-10-06 12:38:26</t>
+    <t>2025-06-12 19:17:34</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:17:35</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:17:36</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:17:37</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:21:26</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:21:27</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:21:28</t>
+  </si>
+  <si>
+    <t>2025-06-12 19:21:29</t>
+  </si>
+  <si>
+    <t>2025-10-07 11:23:54</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>2025-10-07 11:52:56</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:11:58</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:15:27</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:16:18</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:17:32</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:17:53</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:18:48</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:19:37</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:20:34</t>
+  </si>
+  <si>
+    <t>2025-10-08 12:25:42</t>
+  </si>
+  <si>
+    <t>2025-10-08 15:12:49</t>
   </si>
   <si>
     <t>10/03/2025</t>
   </si>
   <si>
-    <t>2025-10-06 20:17:08</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:09</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:10</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:44</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:45</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:46</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:55</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:56</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:17:57</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:18:22</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:18:23</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:18:24</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:19:48</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:19:50</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:19:51</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:21:20</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:21:21</t>
-  </si>
-  <si>
-    <t>2025-10-06 20:21:22</t>
+    <t>2025-10-08 15:56:31</t>
+  </si>
+  <si>
+    <t>2025-10-08 16:07:49</t>
+  </si>
+  <si>
+    <t>2025-10-08 16:09:39</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:32:12</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:33:35</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:41:02</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:48:21</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:54:59</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:55:09</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:55:22</t>
+  </si>
+  <si>
+    <t>2025-10-08 17:57:39</t>
   </si>
 </sst>
 </file>
@@ -843,8 +825,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1166,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -1191,13 +1174,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -1205,13 +1188,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -1219,13 +1202,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -1233,13 +1216,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -1247,13 +1230,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -1261,13 +1244,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -1275,13 +1258,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>14</v>
@@ -1289,13 +1272,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1303,13 +1286,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>14</v>
@@ -1317,13 +1300,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>15</v>
@@ -1331,13 +1314,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>43</v>
@@ -1345,13 +1328,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1359,13 +1342,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>14</v>
@@ -1373,13 +1356,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1387,13 +1370,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>14</v>
@@ -1401,13 +1384,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>15</v>
@@ -1415,13 +1398,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>43</v>
@@ -1429,13 +1412,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -1443,13 +1426,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>14</v>
@@ -1457,13 +1440,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -1471,13 +1454,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>14</v>
@@ -1485,13 +1468,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>15</v>
@@ -1499,13 +1482,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>43</v>
@@ -1513,13 +1496,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -1527,13 +1510,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>14</v>
@@ -1541,13 +1524,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -1555,13 +1538,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D28">
         <v>14</v>
@@ -1569,13 +1552,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D29">
         <v>15</v>
@@ -1583,13 +1566,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>43</v>
@@ -1597,13 +1580,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -1611,13 +1594,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D32">
         <v>14</v>
@@ -1625,13 +1608,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1639,13 +1622,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D34">
         <v>14</v>
@@ -1653,13 +1636,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D35">
         <v>15</v>
@@ -1667,13 +1650,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D36">
         <v>43</v>
@@ -1681,13 +1664,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -1695,13 +1678,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D38">
         <v>14</v>
@@ -1709,13 +1692,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -1723,13 +1706,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>14</v>
@@ -1737,13 +1720,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <v>15</v>
@@ -1751,13 +1734,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D42">
         <v>43</v>
@@ -1765,13 +1748,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D43">
         <v>8</v>
@@ -1779,13 +1762,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D44">
         <v>14</v>
@@ -1793,13 +1776,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -1807,13 +1790,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D46">
         <v>14</v>
@@ -1821,13 +1804,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D47">
         <v>15</v>
@@ -1835,13 +1818,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1849,13 +1832,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D49">
         <v>8</v>
@@ -1863,13 +1846,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D50">
         <v>13</v>
@@ -1877,13 +1860,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -1891,13 +1874,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D52">
         <v>13</v>
@@ -1905,13 +1888,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D53">
         <v>15</v>
@@ -1919,13 +1902,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>43</v>
@@ -1933,13 +1916,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D55">
         <v>8</v>
@@ -1947,27 +1930,27 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
         <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
         <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -1975,58 +1958,58 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D58">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D59">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D60">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B61" t="s">
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D61">
-        <v>9999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
@@ -2037,21 +2020,21 @@
         <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D62">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B63" t="s">
         <v>65</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -2059,55 +2042,55 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
         <v>65</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D64">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
         <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D65">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
         <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D66">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D67">
         <v>8</v>
@@ -2115,735 +2098,343 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D68">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D70">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D71">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C72" t="s">
         <v>21</v>
       </c>
       <c r="D72">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D73">
-        <v>88888</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D74">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D76">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D77">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
         <v>21</v>
       </c>
       <c r="D78">
-        <v>39</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D79">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D80">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>77</v>
-      </c>
-      <c r="B81" t="s">
-        <v>65</v>
+        <v>91</v>
+      </c>
+      <c r="B81" s="1">
+        <v>45933</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>77</v>
-      </c>
-      <c r="B82" t="s">
-        <v>65</v>
+        <v>92</v>
+      </c>
+      <c r="B82" s="1">
+        <v>45933</v>
       </c>
       <c r="C82" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D82">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>77</v>
-      </c>
-      <c r="B83" t="s">
-        <v>65</v>
+        <v>93</v>
+      </c>
+      <c r="B83" s="1">
+        <v>45933</v>
       </c>
       <c r="C83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D83">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>77</v>
-      </c>
-      <c r="B84" t="s">
-        <v>65</v>
+        <v>94</v>
+      </c>
+      <c r="B84" s="1">
+        <v>45933</v>
       </c>
       <c r="C84" t="s">
         <v>21</v>
       </c>
       <c r="D84">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>78</v>
-      </c>
-      <c r="B85" t="s">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="B85" s="1">
+        <v>45933</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>79</v>
-      </c>
-      <c r="B86" t="s">
-        <v>65</v>
+        <v>96</v>
+      </c>
+      <c r="B86" s="1">
+        <v>45933</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D86">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" t="s">
-        <v>65</v>
+        <v>97</v>
+      </c>
+      <c r="B87" s="1">
+        <v>45933</v>
       </c>
       <c r="C87" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>80</v>
-      </c>
-      <c r="B88" t="s">
-        <v>65</v>
+        <v>98</v>
+      </c>
+      <c r="B88" s="1">
+        <v>45933</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D88">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>80</v>
-      </c>
-      <c r="B89" t="s">
-        <v>65</v>
+        <v>99</v>
+      </c>
+      <c r="B89" s="1">
+        <v>45933</v>
       </c>
       <c r="C89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D89">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>81</v>
-      </c>
-      <c r="B90" t="s">
-        <v>65</v>
+        <v>100</v>
+      </c>
+      <c r="B90" s="1">
+        <v>45933</v>
       </c>
       <c r="C90" t="s">
         <v>21</v>
       </c>
       <c r="D90">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>81</v>
-      </c>
-      <c r="B91" t="s">
-        <v>65</v>
+        <v>4</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>82</v>
-      </c>
-      <c r="B92" t="s">
-        <v>65</v>
-      </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>83</v>
-      </c>
-      <c r="B93" t="s">
-        <v>65</v>
-      </c>
-      <c r="C93" t="s">
-        <v>18</v>
-      </c>
-      <c r="D93">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>83</v>
-      </c>
-      <c r="B94" t="s">
-        <v>65</v>
-      </c>
-      <c r="C94" t="s">
-        <v>19</v>
-      </c>
-      <c r="D94">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" t="s">
-        <v>65</v>
-      </c>
-      <c r="C95" t="s">
-        <v>20</v>
-      </c>
-      <c r="D95">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>83</v>
-      </c>
-      <c r="B96" t="s">
-        <v>65</v>
-      </c>
-      <c r="C96" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>84</v>
-      </c>
-      <c r="B97" t="s">
-        <v>65</v>
-      </c>
-      <c r="C97" t="s">
-        <v>22</v>
-      </c>
-      <c r="D97">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
-        <v>85</v>
-      </c>
-      <c r="B98" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
-        <v>86</v>
-      </c>
-      <c r="B99" t="s">
-        <v>88</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>87</v>
-      </c>
-      <c r="B100" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>89</v>
-      </c>
-      <c r="B101" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
-        <v>90</v>
-      </c>
-      <c r="B102" t="s">
-        <v>88</v>
-      </c>
-      <c r="C102" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A103" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103" t="s">
-        <v>88</v>
-      </c>
-      <c r="C103" t="s">
-        <v>22</v>
-      </c>
-      <c r="D103">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
-        <v>92</v>
-      </c>
-      <c r="B104" t="s">
-        <v>88</v>
-      </c>
-      <c r="C104" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A105" t="s">
-        <v>93</v>
-      </c>
-      <c r="B105" t="s">
-        <v>88</v>
-      </c>
-      <c r="C105" t="s">
-        <v>21</v>
-      </c>
-      <c r="D105">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A106" t="s">
-        <v>94</v>
-      </c>
-      <c r="B106" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" t="s">
-        <v>22</v>
-      </c>
-      <c r="D106">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A107" t="s">
-        <v>95</v>
-      </c>
-      <c r="B107" t="s">
-        <v>88</v>
-      </c>
-      <c r="C107" t="s">
-        <v>20</v>
-      </c>
-      <c r="D107">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A108" t="s">
-        <v>96</v>
-      </c>
-      <c r="B108" t="s">
-        <v>88</v>
-      </c>
-      <c r="C108" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A109" t="s">
-        <v>97</v>
-      </c>
-      <c r="B109" t="s">
-        <v>88</v>
-      </c>
-      <c r="C109" t="s">
-        <v>22</v>
-      </c>
-      <c r="D109">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A110" t="s">
-        <v>98</v>
-      </c>
-      <c r="B110" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" t="s">
-        <v>20</v>
-      </c>
-      <c r="D110">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A111" t="s">
-        <v>99</v>
-      </c>
-      <c r="B111" t="s">
-        <v>88</v>
-      </c>
-      <c r="C111" t="s">
-        <v>21</v>
-      </c>
-      <c r="D111">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A112" t="s">
-        <v>100</v>
-      </c>
-      <c r="B112" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" t="s">
-        <v>22</v>
-      </c>
-      <c r="D112">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A113" t="s">
-        <v>101</v>
-      </c>
-      <c r="B113" t="s">
-        <v>88</v>
-      </c>
-      <c r="C113" t="s">
-        <v>20</v>
-      </c>
-      <c r="D113">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A114" t="s">
-        <v>102</v>
-      </c>
-      <c r="B114" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" t="s">
-        <v>21</v>
-      </c>
-      <c r="D114">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A115" t="s">
-        <v>103</v>
-      </c>
-      <c r="B115" t="s">
-        <v>88</v>
-      </c>
-      <c r="C115" t="s">
-        <v>22</v>
-      </c>
-      <c r="D115">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A116" t="s">
-        <v>104</v>
-      </c>
-      <c r="B116" t="s">
-        <v>88</v>
-      </c>
-      <c r="C116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A117" t="s">
-        <v>105</v>
-      </c>
-      <c r="B117" t="s">
-        <v>88</v>
-      </c>
-      <c r="C117" t="s">
-        <v>21</v>
-      </c>
-      <c r="D117">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A118" t="s">
-        <v>106</v>
-      </c>
-      <c r="B118" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" t="s">
-        <v>22</v>
-      </c>
-      <c r="D118">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A119" t="s">
-        <v>66</v>
-      </c>
-      <c r="B119" t="s">
-        <v>67</v>
-      </c>
-      <c r="C119" t="s">
-        <v>68</v>
-      </c>
-      <c r="D119" t="s">
-        <v>69</v>
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup copies="0" horizontalDpi="0" orientation="portrait" paperSize="0" verticalDpi="0"/>
+  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>date</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>2025-10-08 17:57:39</t>
+  </si>
+  <si>
+    <t>2025-10-08 22:17:17</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -2420,15 +2423,29 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="1">
+        <v>45937</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
         <v>4</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C92" t="s">
         <v>6</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D92" t="s">
         <v>7</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>2025-10-08 22:17:17</t>
+  </si>
+  <si>
+    <t>2025-10-08 22:31:42</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -2437,15 +2440,29 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
         <v>4</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>6</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>7</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>date</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>2025-10-08 22:31:42</t>
+  </si>
+  <si>
+    <t>2025-10-08 22:32:41</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -2454,15 +2457,29 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
         <v>4</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>6</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D94" t="s">
         <v>7</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>date</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>2025-10-08 22:32:41</t>
+  </si>
+  <si>
+    <t>2025-10-09 09:27:48</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.19921875"/>
@@ -2471,15 +2474,29 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" t="s">
         <v>6</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>7</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\14-MarquisBook\excel_dockers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{742184C8-01E5-4643-B34C-3646EE469B1E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{904D0D1A-C648-49D3-8005-1255244D099C}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="15720" windowWidth="29040" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>date</t>
   </si>
@@ -207,6 +207,78 @@
   </si>
   <si>
     <t>2025-10-15 09:33:01</t>
+  </si>
+  <si>
+    <t>2025-10-15 14:50:32</t>
+  </si>
+  <si>
+    <t>2025-10-15 14:50:33</t>
+  </si>
+  <si>
+    <t>2025-10-15 14:50:34</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:26:42</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:26:43</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:26:44</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:26:45</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:27:36</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:27:37</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:27:38</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:27:39</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:29:30</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:29:31</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:29:32</t>
+  </si>
+  <si>
+    <t>2025-10-15 17:29:33</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:10:08</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:10:09</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:11:28</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:11:29</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:11:30</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:36:53</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:36:54</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:37:17</t>
+  </si>
+  <si>
+    <t>2025-10-16 10:37:22</t>
   </si>
 </sst>
 </file>
@@ -690,9 +762,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1014,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.140625"/>
@@ -2425,15 +2498,603 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>56</v>
+      </c>
+      <c r="B101" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C102" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C103" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C104" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>58</v>
+      </c>
+      <c r="B106" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>59</v>
+      </c>
+      <c r="B107" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>60</v>
+      </c>
+      <c r="B108" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C108" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>60</v>
+      </c>
+      <c r="B109" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C109" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>61</v>
+      </c>
+      <c r="B111" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>63</v>
+      </c>
+      <c r="B113" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C114" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C115" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>65</v>
+      </c>
+      <c r="B116" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>65</v>
+      </c>
+      <c r="B117" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C117" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>66</v>
+      </c>
+      <c r="B118" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>67</v>
+      </c>
+      <c r="B119" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>67</v>
+      </c>
+      <c r="B120" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C120" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C121" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>68</v>
+      </c>
+      <c r="B122" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C122" t="s">
+        <v>20</v>
+      </c>
+      <c r="D122">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>69</v>
+      </c>
+      <c r="B123" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C123" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>70</v>
+      </c>
+      <c r="B124" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C126" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>72</v>
+      </c>
+      <c r="B127" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>72</v>
+      </c>
+      <c r="B128" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C128" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>72</v>
+      </c>
+      <c r="B129" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C129" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>72</v>
+      </c>
+      <c r="B130" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>73</v>
+      </c>
+      <c r="B131" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>73</v>
+      </c>
+      <c r="B132" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C132" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>74</v>
+      </c>
+      <c r="B133" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C133" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C134" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>74</v>
+      </c>
+      <c r="B135" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C135" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>75</v>
+      </c>
+      <c r="B136" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B137" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B138" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C138" t="s">
+        <v>18</v>
+      </c>
+      <c r="D138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B139" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C139" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B140" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C140" t="s">
+        <v>20</v>
+      </c>
+      <c r="D140">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B141" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C141" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B142" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C143" t="s">
         <v>6</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D143" t="s">
         <v>7</v>
       </c>
     </row>

--- a/resume_template.xlsx
+++ b/resume_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>date</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>2025-10-16 10:37:22</t>
+  </si>
+  <si>
+    <t>2025-10-17 11:03:04</t>
+  </si>
+  <si>
+    <t>2025-10-17 11:03:05</t>
+  </si>
+  <si>
+    <t>2025-10-17 11:03:06</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="24.140625"/>
@@ -3086,15 +3095,99 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B143" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B144" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C144" t="s">
+        <v>18</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B145" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B146" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C146" t="s">
+        <v>20</v>
+      </c>
+      <c r="D146">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B147" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C147" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B148" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C149" t="s">
         <v>6</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D149" t="s">
         <v>7</v>
       </c>
     </row>
